--- a/examples/07-pivot-table.xlsx
+++ b/examples/07-pivot-table.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId2"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -146,7 +147,47 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" refreshOnLoad="1" recordCount="4" r:id="rId1">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:B5" sheet="Data"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="Category" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="2">
+        <s v="Fruit"/>
+        <s v="Veg"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
+      <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1" maxValue="4"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4">
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="4"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4">
   <r>
     <x v="0"/>
@@ -199,6 +240,43 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Amount" fld="1" subtotal="sum" showDataAs="normal" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Counts" cacheId="1" dataOnRows="0" dataCaption="Values" showError="0" showMissing="1" updatedVersion="6" minRefreshableVersion="3" asteriskTotals="0" showItems="1" editData="0" disableFieldList="0" showCalcMbrs="1" visualTotals="1" showMultipleLabel="1" showDataDropDown="1" showDrill="1" printDrill="0" showMemberPropertyTips="1" showDataTips="1" enableWizard="1" enableDrill="1" enableFieldProperties="1" preserveFormatting="1" useAutoFormatting="0" pageWrap="0" pageOverThenDown="0" subtotalHiddenItems="0" rowGrandTotals="1" colGrandTotals="1" fieldPrintTitles="0" itemPrintTitles="0" mergeItem="0" showDropZones="1" createdVersion="6" indent="0" showEmptyRow="0" showEmptyCol="0" showHeaders="1" compact="1" outline="1" outlineData="1" compactData="1" published="0" gridDropZones="0" immersive="1" multipleFieldFilters="0" chartFormat="0" fieldListSortAscending="0" mdxSubqueries="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" r:id="rId1">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showDropDowns="1" compact="1" outline="1" subtotalTop="1" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+      <items count="3">
+        <item t="data" sd="1" x="0"/>
+        <item t="data" sd="1" x="1"/>
+        <item t="default" sd="1"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showDropDowns="1" compact="1" outline="1" subtotalTop="1" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i t="data" r="0" i="0">
+      <x v="0"/>
+    </i>
+    <i t="data" r="0" i="0">
+      <x v="1"/>
+    </i>
+    <i t="grand" r="0" i="0">
+      <x v="0"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i t="data" r="0" i="0"/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Amount" fld="1" subtotal="count" showDataAs="normal" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
 </pivotTableDefinition>
@@ -585,4 +663,67 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Orders per category (a second pivot table on the same cache)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Row Labels</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Count of Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Veg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>